--- a/excel/distribuidora-sol-del-valle-s-a-c_ruta_proxima_semana.xlsx
+++ b/excel/distribuidora-sol-del-valle-s-a-c_ruta_proxima_semana.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rutas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rutas'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rutas'!$A$1:$J$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,11 +57,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,19 +428,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,8 +495,7496 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>C001571875</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>77342050</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ESQUIVEL SANCHEZ LITA IBET</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>MZA CH , LOTE NRO. 3 URB. BARRIO 3 ALTO TRUJILLO La Libertad-Trujillo-El Porvenir</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>C001327968</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>19084482</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>AREDO ANTICONA ENMA LUCILA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>AV. MZ CH LT NRO. 16 URB. ALTO TRUJILLO BARRIO 3 La Libertad-Trujillo-El Porvenir</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>C001740645</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>48109143</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ GUTIERREZ JENNY MARIOLA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>AV. MZ J LOTE NRO. 17 URB. ALTO TRUJILLO BARRIO 2A La Libertad-Trujillo-El Porvenir</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>C001735963</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>41776273</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>GARCIA GONZALEZ LECI MARILU</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>AV. MZ D LOTE NRO. 22 URB. ALTO TRUJILLO BARRIO 2B La Libertad-Trujillo-El Porvenir</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>C001583159</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>43247274</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MOYA VEGA YAQUI ROXANA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>AV. MZA 4 , LOTE NRO. 2 URB. BARR 3 B ALTO TRUJILLO La Libertad-Trujillo-El Porvenir</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>C004184151</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>45116265</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>BILLOTA SANTOS DELIA JACKELINE</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>MZA. Y , LOTE 17 SEC. 3C , ALTO TRUJILLO-EL PORVENIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>C004177207</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>44907086</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>RONDON VALLE MARTHA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>MZA. F , LOTE 24 , BARRIO 3C , ALTO TRUJILLO-EL PORVENIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>C001732191</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>19099476</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ZAVALETA CASTAÑEDA OLGA ELOISA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CL. INDONECIA,MZY,LT NRO. 4 URB. ALTO TRUJILLO BARRIO 2A La Libertad-Trujillo-El Porvenir</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>C001510834</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>80560458</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MENDOZA BENITES DIANA RAQUEL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>AV. MZA A' , LOTE NRO. 33 URB. BARRIO 2A ALTO TRUJILLO La Libertad-Trujillo-El Porvenir</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>C001716495</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19562770</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FLORES SANCHEZ VIRGINIA NATIVIDAD</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>AV. MZA A , LOTE NRO. 25 URB. BARRIO 2- ALTO TRUJILLO La Libertad-Trujillo-El Porvenir</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>C004209466</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8171396</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>BLAS SANCHEZ DE SANCHEZ LUZ MARIA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>MZA. T , LOTE 1 BARRIO 2A , ALTO TRUJILLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>C001737285</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>80137820</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GUTIERREZ AVILA ZULY JANETH</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>AV. MZ K LT NRO. 4 URB. ALTO TRUJILLO BARRIO 1 La Libertad-Trujillo-El Porvenir</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>C001732066</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18981289</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>IPARRAGUIRRE DAVILA LORGIO JOVINO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>AV. MZW,LT16A NRO. 16 URB. ALTO TRUJILLO BARRIO 1 La Libertad-Trujillo-El Porvenir</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>C004167851</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>43651230</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>VARAS HERNANDEZ HIMELINA ARANCEL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>MZA, LL , LOTE 30 , BARRIO 1 ALTO TRUJILLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>C001413893</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19051873</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MINCHOLA VELARDE ERCILA YESENIA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>AV. MZT LT NRO. 8 URB. ALTO TRUJILLO BARRIO 1A La Libertad-Trujillo-El Porvenir</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>C001737406</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>77910312</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SEGURA BRICEÑO ALEJANDRINA THALIA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>AV. MZ B2 LT NRO. 2 URB. ALTO TRUJILLO BARRIO 1A La Libertad-Trujillo-El Porvenir</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>C001417686</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>19055554</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ROJAS ROJALES JUAN AURELIO</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>MZ C, LT NRO. 21 URB. NUEVO JERUSALEN La Libertad-Trujillo-El Porvenir</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>C001567659</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>46765259</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VEGA VILLAVICENCIO ROSA SOFIA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>AV. MZA H , LOTE NRO. 4 URB. NVOJERUSALEN ALTO TRUJILLO La Libertad-Trujillo-El Porvenir</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C001485387</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>46950709</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VALDERRAMA ARANDA CHELA SUSANA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>AV. MZA H LOTE NRO. 36 URB. NUEVO JERUSALEM - ALTO TRUJILL La Libertad-Trujillo-El Porvenir</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C004168393</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>70896973</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ VEGA GLORIA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>MZA. A , LOTE 12 , NUEVO JESUS DE NAZARET, EL PORVENIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C004205087</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>41905736</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>GUZMAN RONDON IRIS VANESSA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>MDO. STA. ROSA , PTO. S/N , MANUEL SEOANE , ESPERANZA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>C001407689</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>80520418</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CALDERON CERNA CARMEN</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>MCDO. LEONCIO PRADO D NRO. 49 URB. LA ESPERANZA La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>C001407681</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>17982999</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>PEREZ MENDOZA BENEDICTO ZACARIAS</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>MCDO. LEONCIO PRADO PSTO NRO. 167 URB. SECTOR MANUEL SEOANE La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>C001438989</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>18156286</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>BOCANEGRA LOZANO LUZ VELINDA</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>MZA H LOTE 21 II ETAPA URB. LOS LAURELES ALTO TRUJILLO La Libertad-Trujillo-El Porvenir</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>C004238092</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>10701920151</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ROMERO OLIVARES MARY CARMEN</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>AV. PROGRESO S/N(MDO.LOS PORTALES , PTO.170) LOS PORTALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>C004184279</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>17942154</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>CARMONA FERNANDEZ JUAN GUILLERMO</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>MERCADO LOS PORTALES , PTO. # 139-LOS PORTALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>C001578141</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>41415393</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>VARELA PERALTA MIGUEL ANGEL</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>MCDO. LOS PORTALES , PTO NRO. 133 URB. LOS PORTALES La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>C001754141</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>19091506</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>CASTILLO CUEVA ANA MELVA</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>MCDO. MCDOLOS PORTALES , PTO NRO. 161 URB. LOS PORTALES La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>C001490410</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>41774397</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>PAREDES ARTEAGA HILDA ELIZABETH</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>MCDO. LOS PORTALES PTO NRO. 323 URB. TRUJILLO La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>C001224103</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>47668993</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>GUZMAN GUZMAN JHON ESMIT</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>MDOLOS PORTALES , PTO 10 URB. LOS PORTALES La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>C004168312</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>18093586</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>LUJAN RODRIGUEZ CARMEN IMELDA</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>LOS JAZMINES , MZA. G , LOTE 19 , LA RINCONADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>C004169843</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>19535149</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>IBAÑEZ VILLALVA FELICIANA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>MZA. G , LOTE 34 HUERTA BELLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>C004060182</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>19084757</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>CRUZ SILVESTRE ENRIQUE AGAPITO</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>MRDO. RINCONADA PTO C 126 , URB. RINCONADA - TRUJILLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>C001122928</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>17943393</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>MENDOCILLA GUTIERREZ CLARISA AMPARO</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>MCDO RINCONADA P22 URB. RINCONADA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>C004243941</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>18154834</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>LOPEZ PLACENCIA MARIA LUZ</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>MERCADO RINCONADA , PTO. 30 , LA RINCONADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>C001733670</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>71276116</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ZAVALETA ACEVEDO MERYL STHEFANIA</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>AV. CESAR VALLEJO,MZC- LT NRO. 46 URB. LA RINCONADA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>C004240529</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>19693987</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>GUEVARA GOMEZ LUIS EFREN</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>LOS ZAFIROS # 693 , LA RINCONADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>C004243706</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>18021359</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>OCHOA LOZADA MIGUEL ANGEL</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>LAS CÁLIDAS ., MZA .37 , LOTE 13, LA RINCONADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>C001579801</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>75503748</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>GUZMAN GERONIMO BHILAR ESMERALDA</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>CL. GRADILEAS , MZA A , LOTE NRO. 2 URB. EL HUERTO La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>C001398489</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>17911462</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>BOCANEGRA ZAVALETA DE CABRERA CHARITO AM</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>AV. LAS PONAS , MZA 69 , LOTE NRO. 22 URB. LA RINCONADA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>C001713388</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>10724567202</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>CAMPOS SALDAÑA KEIKO MARILUS</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>CL. LAS PONAS MZA. 52 LOTE. 59 URB. LA RINCONADA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>C001705333</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>19073671</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ZAVALETA VENTURA SANTOS ESTHER</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>CL. LAS PONAS , MZA52 , LOTE NRO. 53 URB. LA RINCONADA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>C004047648</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>10182168519</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ANDRADE COSSA CESAR ORLANDO</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>PASAJE JULIO C. TELLO 580 URB. CHIMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>C004206783</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>18150963</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>PRINCIPE VASQUEZ BLANCA ELENA</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>GODOFREDO GARCIA # 400 , INT. 3 , CHIMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>C001752122</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>80299999</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>MEDRANO GARCIA LUZ ANGELICA</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>CL. OSWALDO HERCELLES NRO. 204 URB. CHIMU La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>C004244160</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>17866104</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>MORALES OBESO DE LOPEZ NANCY GLADYS</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>WASHINGTON # 108 , LA MARQUEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>C004223304</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>18041579</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>FLORIANO PEREZ SANTOS JUANA</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>LOS GRANATES 158, TRUJILLO 13007, PERÚ</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>C001676516</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>46151177</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>FLORES QUIÑONES KATIA ELIZABET</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>AV. 5 DE ABRIL , MZA 8 , LOTE NRO. 13 URB. PESQUEDA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>C001706176</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>46696766</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>MORENO BARRIOS ENMA MARIBEL</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>MCDO. MCDOCHIMAR , PTO NRO. 7 URB. LOS GRANADOS La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>C004239225</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>18180240</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>RAMOS GIL DE OTINIANO SILVIA EMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>MERCADO CHIMAR , PUESTO , S/N LOS GRANADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>C004184884</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>18101500</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ AVALOS VIOLETA HAYDE</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>MERCADO CHIMAR , PTO. 44-110 , LOS GRANADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>C001122799</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>17804719</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>VALDERRAMA PAREDES EUGENIO BACILIO</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>MCDO. MCDO GRAN CHIMAR PTO NRO. 79 URB. GRANADOS La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>C001122797</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>18094047</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>CESPEDES BARBARAN GLADYS MIRNA</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>MCDO. GRAN CHIMAR PTO NRO. 15 URB. URB GRANADOS La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>C001765856</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>48771293</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>BAZAN QUISPE AMIE NICOLE</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>MCDO. MDOACHIMAR ,PTO NRO. 25 URB. LOS GRANADOS La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>C004184874</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>10178678286</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>OTINIANO ALVARADO LUCIO EFREN</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>HIPOLITO UNANUE # 430 ( MERCADO CHIMAR, PTO.68) , LOS GRANADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>C001568463</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>47126070</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>PRADO BURGOS LESLY ELIZABETH</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>AV. OSWALDO HERCELLES NRO. 374 URB. CHIMU La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>C001736160</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>10444047050</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>GIL TAMAYO CYNTHIA JOSELYN</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>JR. SEBASTIAN BARRANCA NRO. 331 URB. NUEVA MARQUEZA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>C001156665</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>40555832</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>DE LA CRUZ ABURTO ELY LIDIA</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>MDOVILLARREAL PTO170 URB. CHIMU La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>C001668237</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>18168634</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>GERVACIO CARRANZA MARIA LIDIA</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>MCDO. MDOVILLARREAL , PTO A NRO. 139 URB. LOS GRANADOS La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>C004240951</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>72652826</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>FERNANDEZ JUAREZ ROMINA ISABEL</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>JUAN DE LA CIERVA # 155, URB. PAY PAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>C001453484</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>18072271</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>MEDINA VIDAL ELMER ELI</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>AV. EL EJERCITO NRO. 1194 URB. EL MOLINO La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>C001415201</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>10466898304</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>VILLENA CAMPOS ANTONY</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>AV. SANTA NRO. 1141 INT. 3 URB. LA INTENDENCIA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>C001127517</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>20481481156</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>MINIMARKET SAN MARCOS S.A.C.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>AV. AVE EL EJERCITO N865 NRO. 865 MZA. MAZAA013 URB. MOLINO La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>C004168494</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>19421491</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>CHAVEZ ARGOMEDO NORMANDI DORITZA</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>JR. UNION # 900 ARANJUEZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>C001383862</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>10178793743</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>GAMBOA CARRANZA GREGORIO BERNARDO</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>JR. UNION NRO. 939 URB. LA INTENDENCIA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>C001155935</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>43154322</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>GONZALES CASTILLO FANNY RAQUEL</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>MDOEULALIA PTO40 URB. LA NORIA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>C004095441</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>20613687387</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>MINIMARKET LA YAPA S.A.C.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>El Porvenir (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>PJ. MANZANA G LOTE 12 NRO. 9 NUEVO PORVENIR La Libertad-Trujillo-El Porvenir</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>C004241531</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>77986869</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>LOYOLA ROSALES LEYDSIN DAYANA</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>CALLE LOS PINOS , MZA. 9, LOTE 18 LA RINCONADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>C001648623</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>10772848205</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>MORALES SANTISTEBAN JUAN JULLINHOS</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>CL. LOS CIPRECES MZA. 17 LOTE. 14 URB. LA RINCONADA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>C004054187</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>47185267</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>CRUZADO GUEVARA KATHERINE STEFANY</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>LOS CIPRESES 390 - LA RINCONADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>C001675140</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>75689962</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>PEREZ RAMOS ALEX DANIEL</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>CL. LOS CEDROS MZA60, LOTE NRO. 14 URB. LA RINCONADA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>C001635400</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>19084067</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>GUZMAN RAMIREZ WILLY</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>AV. LOS LAURELES ,MZA B , LT18- NRO. 6 URB. SEMI RUSTICA MAMPUESTO La Libertad-Trujillo-Florencia de Mora</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>C001404278</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>80319521</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>SANCHEZ BENITES ESTELA KELI</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>AV. 5 DE ABRIL MZ4, LT NRO. 9 URB. LA PESQUEDA SECTOR 3 La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>C001389150</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>10180750202</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>GALLOSO QUEPQUE SARA AUXILIA</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>AV. 5 DE ABRIL/MZA7,LOTE NRO. 12 MZA. 875 URB. PESQUEDA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>C004167117</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>19066780</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>CRUZ CORCUERA FLOR DALILA</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>AV. 5 DE ABRIL, MZA. 20 , LOTE 9 , PESQUEDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>C001730655</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>10769850207</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>CASTILLO ROJAS LUIS DAVID</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>LUIS DE LA PUENTE UCEDA P MZA. 15 LOTE. 7 URB. CERROR PESQUEDA BARRIO 1 La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>C001567503</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>19669555</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>CABALLERO ALAYO MANUEL ANGEL</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>MCDO. MDO EL BOSQUE , PTO NRO. 45 URB. EL BOSQUE La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>C001437878</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>18143177</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>VIGO DE PLASENCIA ROSA YSABEL</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>CL. ARISTOTELES NRO. 320 URB. LA NORIA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>C001179589</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>10181229832</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>FALLA CABANILLAS MARCO TULIO</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>CL. LUCIO SENECA NRO. 179 URB. LA NORIA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>C001218973</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>17964202</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>SANCHEZ CHAVEZ DE TAMAYO MIRIA ETELVINA</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>MDOLA NORIA , PTO63 URB. LA NORIA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>C001714235</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>43617417</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>BENITES CASTAÑEDA MARITZA PATRICIA</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>AV. GUZMAN BARRON NRO. 558 URB. SANTO DOMINGUITO La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>C001549900</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>73811750</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>GUTIERREZ BOADO ASHLING DAYAN</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>CL. LUIS MONTERO , MZA I , LOTE NRO. 23 URB. SANTO DOMINGUITO La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>C004236870</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>70220270</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>HUERTAS ZARATE ROSA ANGELA</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>CALLE PANCHO FIERRO # 237 , STO. DOMINGUITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>C004238098</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>43867517</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>SANCHEZ GARCIA MARIA ELENA</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>AMERICA SUR # 1087, URB. STO. DOMINGUITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>C001123452</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>18189770</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>RUIZ POLO ELISA SAVINA</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>CL. ALBERTO URETA NRO. 343 URB. PALERMO La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>C001524878</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>75862376</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ARANEDA JAUREGUI HECTOR LUIS</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>CL. SANTOS CHOCANO NRO. 410 URB. PALERMO La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>C001568832</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>45048481</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>CHAVEZ REQUELME GIANCARLOS ELISEO</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>MCDO. MDO UNION , PTO NRO. 128 INT. A URB. INTENDENCIA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>C001453490</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>74969823</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>SANCHEZ ARCE VICTOR JAVIER</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>AV. MANTARO 610 NRO. 614 URB. EL MOLINO La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>C001621499</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>10436597270</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>JULCA BARRETO ESTHER ADELINA</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>CL. W TORRES ORTEGA NRO. 955 URB. MIRAFLORES La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>C001512341</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>10700432268</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>CACHIQUE CACHIQUE NEY FROLLAN</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>PJE. PACASMAYO NRO. 311 URB. ARANJUEZ La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>C001765008</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>48313919</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>AYALA JARA DANIELA LETICIA</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>CL. CHICLAYO NRO. 272 URB. ARANJEZ La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>C001732948</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>73329969</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SANCHEZ AMAYA WHITNEY STEFANI</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>JR. BASILIO PACHECO NRO. 588 URB. EL BOSQUE La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>C004241787</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>44310555</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>CASTILLO CORDOVA STEVEN JAMES</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>CALLE . SIMON BOLIVAR , MZA. P , LOTE 10, SEMIRUSTICA EL BOSQUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>C001123409</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>17833432</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SARE DE LA CRUZ JORGE MARINO</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>MCDO STO DOMINGUITO P-22 - 23 URB. STO DOMINGUITO La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>C001128847</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>42501344</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>RUBINA SANCHEZ DENIS MARITZA</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>PJE. MIGUEL ANGEL NRO. 018 URB. SANTO DOMINGUITO La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>C004240775</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>17920222</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>RIOS DE REYES PETRONILA IRIS</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>BACILO PACHECO 327 , EL BOSQUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>C001766895</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>75314817</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>RAMIREZ ARIMUYA ROMARIO</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>MCDO. LA HERMELINDA ,PTOB- NRO. 130 URB. LA HERMELINDA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>C001130042</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>26664417</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>BURGOS VALLEJOS MARIA FLORINDA</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>MCDO LAS QUINTANAS PTO 06 URB. LAS QUINTANAS La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>C004059790</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>20613304721</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIALIZADORA CASA BL</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>AV. TUPAC AMARU NRO. 772 URB. PRIMAVERA ET. 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>C004097281</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>48154502</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>QUISPE CRUZADO LUZ DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>AV.CARLOS VALDERRAMA # 308 LAS QUINTANAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>C001500893</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>10479843916</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>ARENAS RAMOS KIMBERLYN ODETH</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>JR. VIVALDI NRO. 331 URB. PRIMAVERA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>C004166794</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>10180741483</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>CARRASCAL SERRANO JAIME JESUS</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>AVENIDA NICOLAS DE PIEROLA 1230 , SAN FERNANDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>C001663041</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>47006426</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>CARRANZA ALFARO VANIA JUDITH</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>C. MANUEL TEJADA 605 URB. SAN FERNANDO  La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>C004204755</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>10478514196</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>LOPEZ BOCANEGRA HENRY</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>CALLE LEANDRO ALVIÑA # 380 URB. SAN FERNANDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>C001522519</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>17823548</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>DIAZ CHAVEZ RODOLFO ALBERTO</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>CL. CESAR MANRIQUE NRO. 1531 URB. MOCHICA La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>C001640339</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>47622597</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>PAREDES AGUILAR ANNIE ZULEYMA</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>CL. MZA L , LOTE NRO. 9 URB. ALTO MOCHIC II La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>C004237929</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>17995912</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>GONZALEZ RODRIGUEZ YOLANDA</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>CALLE TADEO MONAGAS # 465 , ESPERANZA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>C001402202</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>17821241</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>CORDOVA JULCA ELDA ELISABETH</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>CL. MONAGAS NRO. 570 URB. ESPERANZA ALTA La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>C004240346</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>44633094</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>LIZA ORIBE CINTHIA MARILIN</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>TADEO MONAGAS #631 , LA ESPERANZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>C004236543</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>73309586</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>QUIJANO ZAVALETA INES MARAVY</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>JOSE PAEZ # 1440 LA ESPERANZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>C001328262</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>17990963</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>VASQUEZ DE SAAVEDRA MARIA GUMERCINDA</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>JR. FELIX ALDAO NRO. 654 URB. ESPERANZA ALTA La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>C004236868</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>18887809</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>MIÑANO PORTILLA GLORIA</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>SANTIAGO MARIÑOS # 1637 , ESPERANZA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>C001738900</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>17995781</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>GAITAN CABANILLAS MARIA F</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>CL. FELIX ALDAO NRO. 496 URB. ESPERANZA ALTA La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>C004251171</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>61069823</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>URTECHO GERBACIO LILIANA LIZET</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>ALEXANDER PETTION # 335 ESPERANZA  ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>C004168487</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>10468079858</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>PEREZ HUAMAN DANNY ARTHUR</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>JOSE CASTELLI # 228 ESPERANZA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>C001407567</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>40544608</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>GONZALES JULCA IRIS NOLBERTA</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>AV. 18 DE MAYO NRO. 1901 URB. ESPERANZA ALTA La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>C004186187</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>19083303</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>DIAZ SEPULVEDA SUSANA EDITH</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>MC. GREGOR # 719 , LA ESPERANZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>C001401994</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>10179823182</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>PAREDES VDA. DE LEON MARIA ALICIA</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>AV. BAQUIJANO Y CARRILLO NRO. 1748 URB. LA ESPERANZA La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>C001738982</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>42098775</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>SALINAS SALDAÑA CRISTINA BEATRIZ</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>AV. SANTA ROSA NRO. 789 URB. ESPERANZA ALTA La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>C001683306</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>20609375079</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>FOOD &amp; MARKET PERU S.A.C.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>JR. FRANCISCO PIZARRO NRO. 937 URB. CENTRO CIVICO La Libertad-Trujillo-Trujillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>C001390118</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>10182254261</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>OSORIO POLO ORLANDO JAIME</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>CL. LOS ANGELES/MZA20,LOTE NRO. 21 MZA. 421 URB. ESPERANZA/PARTE ALTA La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>C001736497</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>47924237</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>VILLENA BECERRA SHUSEY ESTEFANY</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>AV. MZA H , LOTE NRO. 28 URB. AHNUEVO JERUSALEN La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>C001676187</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>80639856</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>GOICOCHEA AREVALO JUAN JENINFER</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>MCDO. MCDO ISRAELITA , PTO NRO. 3 URB. ESPERANZA ALTA La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>C001488137</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>10419806663</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>RIOS LEON MIGUEL ANGEL</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>MZA 24 LOTE NRO. 13 URB. AH MANUEL SEOANE La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>C001735336</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>42617795</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>CALDERON VILLANUEVA DORALIZ RAQUEL</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>CL. MAC GREGOR NRO. 902 URB. ESPERANZA CENTRAL BARRIO 4 La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>C001731041</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>44208682</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>BOBADILLA SAENZ TERESA RICARDINA</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>CL. FRANCISCO DE PAULA SANTANDER NRO. 1289 URB. LA ESPERANZA ASOC SAN MARTÍN La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>C001739792</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>41343078</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>ALFARO MUÑOZ MARITZA ESTHER</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>CL. ANTONIO MARIÑOS NRO. 1245 URB. SECSAN MARTIN ESPERANZA ALTA La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>C004214055</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>10180540623</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>VILLAR CUEVA EMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>CALLE JOSE ARTIGAS # 1574 , ESPERANZA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>C001714452</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>16718552</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>SANCHEZ SANTISTEBAN FLOR MARGARITA</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>CL. MANUEL CEDEÑO NRO. 1540 URB. ESPERANZA ALTA La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>C004054047</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>75769716</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>AGREDA RUIZ REBECA MILAGRITOS ESMERALDA</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>MANUEL CEDEÑO 1558 LA ESPERANZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>C001179289</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>18054307</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>ARMAS DE TOCTO MARIA CONVERCION</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>MDOSAN MARTIN , PTO 179 URB. ESPERANZA ALTA La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>C001130068</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>27921418</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>CALDERON RODRIGUEZ WILDER YLARIO</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>MCDO SAN MARTIN PTO 204 URB. ESPERANZA ALTA La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>C001499810</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>18148647</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>CASTILLO NARRO DE BRAVO MAGALI ROSELI</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>MCDO. SAN MARTIN PTO NRO. 85 URB. ESPERANZA ALTA La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>C004061920</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>42609842</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>CARBAJAL PRETEL DANTE AMIN</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>MRDO. SAN MARTIN PTO 205 - LA ESPERANZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>C001500673</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>43594309</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>CRUZ GONZALES NILDA JUDITH</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>MCDO. MCDO SAN MARTIN , PTO NRO. 180 URB. ESPERANZA ALTA La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>C001733708</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>18054136</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>ORTIZ DE RODRIGUEZ IRMA SOLEDAD</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>CL. FRANCISCO DE PAULA NRO. 1122 URB. ESPERANZA ALTA La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>C001371461</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>10465419500</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>BAZAN MOYA LESLIE JULIANA</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>JR. TAHUANTINSUYO NRO. 1600 URB. LA ESPERANZA La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>C001324470</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>18106105</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>PARIMANGO ANTICONA CAROLINA YSABEL</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>JR. MZA 22A ,LOTE NRO. 8 URB. FRATERNIDAD La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>C001732393</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>70291797</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>RENGIFO VERA DALILA MARICELI</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>CL. FRATERNIDAD NRO. 2311 URB. LA ESPERANZA BARRIO 1 La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>C004238516</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>72077375</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>LUJAN LEZAMA JAIR ANTHONY</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>CALLE 22 DE FEBRERO # 1069 ESPERANZA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>C004169210</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>71238731</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>LOZADA GONZALES ANGIE PAOLA</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>22 DE FEBRERO 1024 ESPERANZA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>C004234804</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>18028542</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>TORRES RAMOS MARIA YANE</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>AV.GRAN CHIMU  # 899 , ESPERANZA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>C004236538</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>18127699</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>RIOS YUPANQUI JACINTO DIOMEDES</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Trujillo (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>GRAN CHIMU # 776 , LA ESPERANZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>C001730884</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>18103030</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>AVILA ASUNCION LASTENIA JACINTA</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>La Esperanza (Trujillo)</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>CL. 22 DE FEBRERO NRO. 590 URB. ESPERANZA - ALTA La Libertad-Trujillo-La Esperanza</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:J145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>